--- a/data/trans_orig/P64S_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64S_2023_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según las combinaciones de formas de desplazamiento que utilizan desde su casa al centro de trabajo/estudios en 2023</t>
+          <t>Población según las combinaciones de formas de desplazamiento que utilizan desde su casa al centro de trabajo/estudios en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>955</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10096</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23912</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>859</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11187</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>894</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>929</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2199,12 +2199,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>90798</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110651</t>
+          <t>110865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34664</t>
+          <t>34036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113610</t>
+          <t>111053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142906</t>
+          <t>141226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -2425,12 +2425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23116</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39565</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>36443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59996</t>
+          <t>61212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38006</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95511</t>
+          <t>94102</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49930</t>
+          <t>49334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82251</t>
+          <t>83171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>95839</t>
+          <t>98703</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>168824</t>
+          <t>166433</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15955</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>21152</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42781</t>
+          <t>43040</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42543</t>
+          <t>42104</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80678</t>
+          <t>79341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>15440</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36974</t>
+          <t>35306</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29531</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>59125</t>
+          <t>58811</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>46913</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17250</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36206</t>
+          <t>37144</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>36435</t>
+          <t>34662</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74489</t>
+          <t>74706</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>55743</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>59633</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>57767</t>
+          <t>56402</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>101474</t>
+          <t>104046</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -4124,12 +4124,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>930498</t>
+          <t>929812</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1183372</t>
+          <t>1190448</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>361258</t>
+          <t>358812</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>522260</t>
+          <t>523569</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1337701</t>
+          <t>1338544</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1706897</t>
+          <t>1732379</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20027</t>
+          <t>19993</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>273910</t>
+          <t>278317</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>321839</t>
+          <t>344249</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>77212</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>186924</t>
+          <t>188244</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>164303</t>
+          <t>164497</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>244508</t>
+          <t>245203</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>254937</t>
+          <t>236484</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>421045</t>
+          <t>422165</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>942</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>812</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>34733</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>56112</t>
+          <t>55961</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>54438</t>
+          <t>55111</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>81640</t>
+          <t>81705</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5206</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16268</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>30730</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6613</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20350</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>16062</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>33926</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5710,12 +5710,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>27271</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>54292</t>
+          <t>54464</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>31943</t>
+          <t>31520</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>47314</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>78911</t>
+          <t>78126</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -5823,12 +5823,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5936,12 +5936,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>7706</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>32346</t>
+          <t>31650</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -6049,12 +6049,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>238084</t>
+          <t>241654</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>285654</t>
+          <t>288299</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>214581</t>
+          <t>215471</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>251497</t>
+          <t>250166</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>467822</t>
+          <t>463977</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>523827</t>
+          <t>525531</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>18438</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -6275,12 +6275,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>63122</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>94935</t>
+          <t>95183</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>75968</t>
+          <t>75809</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>105945</t>
+          <t>104660</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>145906</t>
+          <t>144750</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>186788</t>
+          <t>189768</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>933</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>784</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>62584</t>
+          <t>59478</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>121260</t>
+          <t>120494</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>93234</t>
+          <t>93061</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>133615</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>164063</t>
+          <t>166036</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>244230</t>
+          <t>243802</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>59670</t>
+          <t>58941</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>35623</t>
+          <t>35389</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>71049</t>
+          <t>69969</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>68825</t>
+          <t>69270</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>118320</t>
+          <t>113188</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -7183,12 +7183,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>12535</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>17496</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -7409,12 +7409,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>22829</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>52320</t>
+          <t>51244</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>26473</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>47994</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>53133</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>91100</t>
+          <t>92112</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -7522,12 +7522,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7537,49 +7537,49 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>4649</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>11657</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>4649</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>10226</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -7592,12 +7592,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>22209</t>
+          <t>22117</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>44672</t>
+          <t>45625</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>94785</t>
+          <t>95033</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>39266</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>65667</t>
+          <t>66571</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>93618</t>
+          <t>96000</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>150771</t>
+          <t>153737</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>18299</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -7861,12 +7861,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>29119</t>
+          <t>29108</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>63659</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>47679</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>80512</t>
+          <t>81489</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7931,12 +7931,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>83437</t>
+          <t>83856</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>134069</t>
+          <t>136985</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1288645</t>
+          <t>1294023</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1572412</t>
+          <t>1587774</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>615444</t>
+          <t>607047</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>784909</t>
+          <t>781015</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8024,12 +8024,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>1964847</t>
+          <t>1959257</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2423929</t>
+          <t>2390274</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>69,84%</t>
         </is>
       </c>
     </row>
@@ -8087,12 +8087,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>27527</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8122,12 +8122,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>328310</t>
+          <t>301183</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8137,12 +8137,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>21925</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>356969</t>
+          <t>372097</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -8200,12 +8200,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>158410</t>
+          <t>153359</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>286980</t>
+          <t>281596</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8235,12 +8235,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>280272</t>
+          <t>278443</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>369256</t>
+          <t>367733</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8270,12 +8270,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>443235</t>
+          <t>441771</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>641164</t>
+          <t>638947</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64S_2023_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64S_2023_R-Estudios-trans_orig.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>912</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>912</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11187</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1978,12 +1978,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>867</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2116,32 +2116,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2151,32 +2151,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -2194,32 +2194,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>101699</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90798</t>
+          <t>96582</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110865</t>
+          <t>125631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>76,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2229,32 +2229,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>29599</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>38842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2264,32 +2264,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>127536</t>
+          <t>142315</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111053</t>
+          <t>125467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>141226</t>
+          <t>158882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>63,07%</t>
         </is>
       </c>
     </row>
@@ -2307,32 +2307,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2377,32 +2377,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -2420,32 +2420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>15092</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27157</t>
+          <t>37223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2455,32 +2455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>34114</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22980</t>
+          <t>26233</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2490,32 +2490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>47699</t>
+          <t>58515</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36443</t>
+          <t>45408</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61212</t>
+          <t>73155</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132103</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,17 +2568,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>87996</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>87996</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80447</t>
+          <t>87996</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,17 +2603,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>212550</t>
+          <t>251930</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>72058</t>
+          <t>77815</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38006</t>
+          <t>62199</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>94102</t>
+          <t>100547</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>67319</t>
+          <t>75513</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49334</t>
+          <t>62369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83171</t>
+          <t>89871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>139376</t>
+          <t>153328</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>98703</t>
+          <t>131313</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>166433</t>
+          <t>177258</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>41083</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43040</t>
+          <t>54031</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>80616</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>42104</t>
+          <t>64268</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>79341</t>
+          <t>101934</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3338,12 +3338,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15440</t>
+          <t>15388</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -3554,32 +3554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3589,32 +3589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20622</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3624,32 +3624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>42668</t>
+          <t>49949</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>26823</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58811</t>
+          <t>70065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -3667,102 +3667,102 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1734</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2779</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>15684</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1802</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>6931</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>6157</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>14989</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -3780,32 +3780,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46913</t>
+          <t>47317</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3815,32 +3815,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>31825</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>22902</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>37144</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>54663</t>
+          <t>64719</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34662</t>
+          <t>50097</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>74706</t>
+          <t>82836</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3893,32 +3893,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3928,32 +3928,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>16816</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3963,32 +3963,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4006,32 +4006,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>47165</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>55743</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4041,32 +4041,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>50946</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>30975</t>
+          <t>38025</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>59633</t>
+          <t>65204</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4076,32 +4076,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>80167</t>
+          <t>98111</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>56402</t>
+          <t>80460</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>104046</t>
+          <t>119426</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4119,32 +4119,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1020538</t>
+          <t>846922</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>929812</t>
+          <t>805187</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1190448</t>
+          <t>887262</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4154,32 +4154,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>465043</t>
+          <t>468225</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>358812</t>
+          <t>441424</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>523569</t>
+          <t>497564</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4189,32 +4189,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1485581</t>
+          <t>1315146</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1338544</t>
+          <t>1267536</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1732379</t>
+          <t>1366779</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>61,68%</t>
         </is>
       </c>
     </row>
@@ -4232,32 +4232,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4267,32 +4267,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>72709</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>278317</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4302,32 +4302,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>82788</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10666</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>344249</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>145170</t>
+          <t>166553</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77212</t>
+          <t>140011</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>188244</t>
+          <t>198372</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4380,32 +4380,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>213628</t>
+          <t>237437</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>164497</t>
+          <t>213099</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>245203</t>
+          <t>262315</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4415,32 +4415,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>358798</t>
+          <t>403990</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>236484</t>
+          <t>364250</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>422165</t>
+          <t>444665</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1382383</t>
+          <t>1270515</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1382383</t>
+          <t>1270515</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1382383</t>
+          <t>1270515</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>944963</t>
+          <t>945272</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>944963</t>
+          <t>945272</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>944963</t>
+          <t>945272</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4528,17 +4528,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2327346</t>
+          <t>2215787</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2327346</t>
+          <t>2215787</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2327346</t>
+          <t>2215787</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -4801,102 +4801,102 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>23898</t>
+          <t>28193</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>19543</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>38789</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>46818</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>37466</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>59849</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>9,81%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>75011</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>62324</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>92489</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
           <t>7,77%</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>44003</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>35060</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>55961</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>67901</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>55111</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>81705</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20096</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,67 +4949,67 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>21849</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>14818</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>33831</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>20365</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>13115</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>31392</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5479,32 +5479,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5514,32 +5514,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>14269</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>21868</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5549,32 +5549,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>24107</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>16062</t>
+          <t>15613</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5627,32 +5627,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5662,32 +5662,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5705,32 +5705,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>46839</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>54464</t>
+          <t>62969</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5740,32 +5740,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>21705</t>
+          <t>23892</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>31520</t>
+          <t>33550</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5775,32 +5775,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>70731</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>47314</t>
+          <t>55149</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>78126</t>
+          <t>92253</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -5818,32 +5818,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5863,12 +5863,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7488</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5888,22 +5888,22 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -5931,32 +5931,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5966,32 +5966,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>13251</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6001,32 +6001,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>21663</t>
+          <t>25955</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>13585</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>36835</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -6044,32 +6044,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>263373</t>
+          <t>281273</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>241654</t>
+          <t>255394</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>288299</t>
+          <t>303744</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>233180</t>
+          <t>251946</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>215471</t>
+          <t>233732</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>250166</t>
+          <t>271515</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6114,32 +6114,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>496553</t>
+          <t>533220</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>463977</t>
+          <t>498829</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>525531</t>
+          <t>562453</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -6157,32 +6157,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6192,32 +6192,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>13833</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6227,32 +6227,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>7650</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>21009</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6270,32 +6270,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>77519</t>
+          <t>82890</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>66104</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>95183</t>
+          <t>100963</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6305,32 +6305,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>88988</t>
+          <t>99692</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>104660</t>
+          <t>116475</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>166506</t>
+          <t>182582</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>144750</t>
+          <t>160514</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>189768</t>
+          <t>207694</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -6383,17 +6383,17 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>447280</t>
+          <t>487571</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>447280</t>
+          <t>487571</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>447280</t>
+          <t>487571</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6418,17 +6418,17 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>435359</t>
+          <t>477476</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>435359</t>
+          <t>477476</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>435359</t>
+          <t>477476</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6453,17 +6453,17 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>882639</t>
+          <t>965048</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>882639</t>
+          <t>965048</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>882639</t>
+          <t>965048</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
@@ -6580,22 +6580,22 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>7519</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>924</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>930</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -6726,32 +6726,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>97671</t>
+          <t>107756</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>59478</t>
+          <t>90436</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>120494</t>
+          <t>127345</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>114299</t>
+          <t>125338</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>93061</t>
+          <t>108270</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>133375</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6796,32 +6796,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>211970</t>
+          <t>233094</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>166036</t>
+          <t>206197</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>243802</t>
+          <t>261837</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -6839,32 +6839,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>53654</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>26505</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>58941</t>
+          <t>72259</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6874,32 +6874,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>56614</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>44497</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>69969</t>
+          <t>72549</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6909,32 +6909,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>91230</t>
+          <t>110268</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>91581</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>113188</t>
+          <t>134333</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
           <t>2,67%</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -7178,32 +7178,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>9973</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7248,32 +7248,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>12535</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>15470</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -7404,32 +7404,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>51244</t>
+          <t>58828</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>47994</t>
+          <t>52242</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7474,32 +7474,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>71392</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>53133</t>
+          <t>64138</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>92112</t>
+          <t>102667</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7517,67 +7517,67 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>6761</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>17432</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>4612</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>11496</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>4649</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>1368</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>11657</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7587,32 +7587,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>11410</t>
+          <t>12392</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -7630,32 +7630,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>71450</t>
+          <t>84135</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>45625</t>
+          <t>64568</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>95033</t>
+          <t>104944</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7665,32 +7665,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>50729</t>
+          <t>60660</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>39266</t>
+          <t>47882</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>66571</t>
+          <t>75163</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7700,32 +7700,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>122179</t>
+          <t>144795</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>96000</t>
+          <t>122509</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>153737</t>
+          <t>171808</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
           <t>3,57%</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7743,102 +7743,102 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>18299</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>8333</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>18849</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>20555</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>12777</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>31974</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>4472</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>1524</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>11566</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>14217</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="inlineStr">
-        <is>
-          <t>7754</t>
-        </is>
-      </c>
-      <c r="T66" s="2" t="inlineStr">
-        <is>
-          <t>24797</t>
-        </is>
-      </c>
-      <c r="U66" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V66" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="W66" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -7856,32 +7856,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>45904</t>
+          <t>59062</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>43977</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>63659</t>
+          <t>77970</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7891,32 +7891,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>63967</t>
+          <t>76627</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>61628</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>81489</t>
+          <t>93913</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7926,32 +7926,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>109871</t>
+          <t>135689</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>83856</t>
+          <t>113097</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>136985</t>
+          <t>160364</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7969,32 +7969,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>1385609</t>
+          <t>1240912</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1294023</t>
+          <t>1185157</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1587774</t>
+          <t>1282448</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8004,32 +8004,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>724061</t>
+          <t>749770</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>607047</t>
+          <t>716278</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>781015</t>
+          <t>786460</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8039,32 +8039,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>2109670</t>
+          <t>1990681</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>1959257</t>
+          <t>1935126</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>2390274</t>
+          <t>2053644</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -8082,32 +8082,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>17257</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>50928</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8117,32 +8117,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>77693</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>301183</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8152,32 +8152,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>94950</t>
+          <t>43906</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>372097</t>
+          <t>64504</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -8195,32 +8195,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>239138</t>
+          <t>273844</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>153359</t>
+          <t>239989</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>281596</t>
+          <t>310406</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8230,32 +8230,32 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>333866</t>
+          <t>371242</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>278443</t>
+          <t>341680</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>367733</t>
+          <t>402727</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8265,32 +8265,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>573003</t>
+          <t>645086</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>441771</t>
+          <t>598399</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>638947</t>
+          <t>695457</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>20,26%</t>
         </is>
       </c>
     </row>
@@ -8308,17 +8308,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>1961766</t>
+          <t>1922022</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1961766</t>
+          <t>1922022</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1961766</t>
+          <t>1922022</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8343,17 +8343,17 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>1460769</t>
+          <t>1510744</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>1460769</t>
+          <t>1510744</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1460769</t>
+          <t>1510744</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8378,17 +8378,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>3422535</t>
+          <t>3432765</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>3422535</t>
+          <t>3432765</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>3422535</t>
+          <t>3432765</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
